--- a/Pricing/Inflación.xlsx
+++ b/Pricing/Inflación.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Mes</t>
   </si>
@@ -110,6 +110,12 @@
   </si>
   <si>
     <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
   </si>
 </sst>
 </file>
@@ -467,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -718,6 +724,22 @@
         <v>0.37</v>
       </c>
     </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>4.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
